--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-18T09:24:58+00:00</t>
+    <t>2025-02-07T10:03:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:03:43+00:00</t>
+    <t>2025-02-07T10:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Property</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:49:13+00:00</t>
+    <t>2025-02-07T11:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ToDo</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -301,26 +304,28 @@
       <c r="A11" t="s" s="2">
         <v>18</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" t="s" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T11:56:07+00:00</t>
+    <t>2025-03-08T15:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T15:01:54+00:00</t>
+    <t>2025-03-08T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-08T16:16:40+00:00</t>
+    <t>2025-03-12T07:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -53,7 +53,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T07:45:08+00:00</t>
+    <t>2025-03-21T10:14:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T13:03:45+00:00</t>
+    <t>2026-01-12T10:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:11:28+00:00</t>
+    <t>2026-01-12T10:18:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:18:34+00:00</t>
+    <t>2026-01-12T10:26:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T10:26:55+00:00</t>
+    <t>2026-01-28T07:37:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:37:37+00:00</t>
+    <t>2026-01-28T07:43:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:43:18+00:00</t>
+    <t>2026-01-28T07:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T07:44:30+00:00</t>
+    <t>2026-01-28T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:46:49+00:00</t>
+    <t>2026-02-24T18:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T18:21:42+00:00</t>
+    <t>2026-02-26T08:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:55:53+00:00</t>
+    <t>2026-03-06T07:38:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T07:38:40+00:00</t>
+    <t>2026-03-06T14:26:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:26:35+00:00</t>
+    <t>2026-03-09T09:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T09:58:26+00:00</t>
+    <t>2026-03-11T09:54:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T09:54:15+00:00</t>
+    <t>2026-03-18T07:58:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T07:58:35+00:00</t>
+    <t>2026-04-07T11:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:55:37+00:00</t>
+    <t>2026-04-08T07:58:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T07:58:25+00:00</t>
+    <t>2026-06-09T13:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:05:25+00:00</t>
+    <t>2026-06-09T13:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T13:44:21+00:00</t>
+    <t>2026-06-09T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T19:55:01+00:00</t>
+    <t>2026-06-10T09:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/TC-FHIR-AG-Scheduling-R5/R5/ValueSet/AtSchedulingServiceType</t>
+    <t>https://fhir.hl7.at/tc/wg/scheduling/r5/ValueSet/AtSchedulingServiceType</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:07:46+00:00</t>
+    <t>2026-08-18T08:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:43:24+00:00</t>
+    <t>2026-08-18T13:20:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T13:20:27+00:00</t>
+    <t>2026-08-31T14:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-main/ValueSet-AtSchedulingServiceType.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:45:12+00:00</t>
+    <t>2026-09-01T07:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
